--- a/SYS_DEV/Columbia/V0/V0.7/v0.7.0/BOM-SPECIES-Columbia-v0.7.0.xlsx
+++ b/SYS_DEV/Columbia/V0/V0.7/v0.7.0/BOM-SPECIES-Columbia-v0.7.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Smart-Penetrometer-with-Edge-Computing-and-Intelligent-Embedded-Systems\SYS_DEV\Columbia\V0\V0.7\v0.7.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slm30\Documents\GitHub\Smart-Penetrometer-with-Edge-Computing-and-Intelligent-Embedded-Systems\SYS_DEV\Columbia\V0\V0.7\v0.7.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797B760F-440A-4854-9B2D-0513B08FDA4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC6B2ED-1071-43B9-908B-581C1DE2BB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
   <si>
     <t>Total Cost</t>
   </si>
@@ -47,9 +47,6 @@
     <t>Component</t>
   </si>
   <si>
-    <t>Amount</t>
-  </si>
-  <si>
     <t>Individual Cost</t>
   </si>
   <si>
@@ -74,15 +71,6 @@
     <t>Total</t>
   </si>
   <si>
-    <t>outer brass tube - spike</t>
-  </si>
-  <si>
-    <t>inner brass tube - spike</t>
-  </si>
-  <si>
-    <t>abs tube for spike</t>
-  </si>
-  <si>
     <t>https://www.grainger.com/product/ABS-Tube-Stock-3-ft-Lg-60CY12?opr=ODOH&amp;analytics=FM:Order%20History</t>
   </si>
   <si>
@@ -101,9 +89,6 @@
     <t>360 Brass Rod: 1/4 in Outside Dia, 4 ft Overall Lg, H02, Mill, 45,000 psi Yield Strength</t>
   </si>
   <si>
-    <t>heat shrink</t>
-  </si>
-  <si>
     <t>https://www.grainger.com/product/SHRINK-KON-Heat-Shrink-Tubing-0-75-in-3KH60?opr=ILOF</t>
   </si>
   <si>
@@ -144,6 +129,36 @@
   </si>
   <si>
     <t>Super Glue</t>
+  </si>
+  <si>
+    <t>outer brass tube - spike probe</t>
+  </si>
+  <si>
+    <t>inner brass tube - spike probe</t>
+  </si>
+  <si>
+    <t>abs tube - spike probe</t>
+  </si>
+  <si>
+    <t>heat shrink - spike probe</t>
+  </si>
+  <si>
+    <t>Gorilla Glue</t>
+  </si>
+  <si>
+    <t>Gorilla Glue Original</t>
+  </si>
+  <si>
+    <t>Used between spike probe layers</t>
+  </si>
+  <si>
+    <t>Gorilla 8 oz. Original Glue 50008A - The Home Depot</t>
+  </si>
+  <si>
+    <t>Amount per Package</t>
+  </si>
+  <si>
+    <t>Amount in Inventory</t>
   </si>
 </sst>
 </file>
@@ -208,7 +223,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -231,6 +246,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -567,23 +585,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M35"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="74" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="69.42578125" customWidth="1"/>
-    <col min="8" max="8" width="76" customWidth="1"/>
-    <col min="9" max="9" width="83.5703125" customWidth="1"/>
-    <col min="10" max="10" width="62.5703125" customWidth="1"/>
-    <col min="11" max="11" width="55.85546875" customWidth="1"/>
-    <col min="12" max="12" width="51" customWidth="1"/>
+    <col min="1" max="1" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="79.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.26953125" customWidth="1"/>
+    <col min="7" max="7" width="41" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="99.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="76" customWidth="1"/>
+    <col min="10" max="10" width="83.54296875" customWidth="1"/>
+    <col min="11" max="11" width="62.54296875" customWidth="1"/>
+    <col min="12" max="12" width="55.81640625" customWidth="1"/>
+    <col min="13" max="13" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
@@ -591,492 +611,544 @@
         <v>2</v>
       </c>
       <c r="C1" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="F1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="8" t="s">
+      <c r="I1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="6">
+        <v>6.57</v>
+      </c>
+      <c r="F2" s="6">
+        <f t="shared" ref="F2:F4" si="0">D2*E2</f>
+        <v>6.57</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="5"/>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="E3" s="6">
+        <v>16.45</v>
+      </c>
+      <c r="F3" s="6">
+        <f t="shared" si="0"/>
+        <v>2.0562499999999999</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="E4" s="6">
+        <v>13.59</v>
+      </c>
+      <c r="F4" s="6">
+        <f t="shared" si="0"/>
+        <v>2.26953</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+    </row>
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="C5" s="2"/>
+      <c r="D5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E5" s="6">
+        <v>7.76</v>
+      </c>
+      <c r="F5" s="6">
+        <f>D5*E5</f>
+        <v>0.77600000000000002</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="5"/>
+    </row>
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="F6" s="6">
+        <f>D6*E6</f>
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="G6" s="6"/>
+      <c r="H6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="6">
+        <v>4.99</v>
+      </c>
+      <c r="F7" s="6">
+        <f>D7*E7</f>
+        <v>4.99</v>
+      </c>
+      <c r="G7" s="6"/>
+      <c r="H7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2">
         <v>1</v>
       </c>
-      <c r="D2" s="6">
-        <v>6.41</v>
-      </c>
-      <c r="E2" s="6">
-        <f t="shared" ref="E2:E4" si="0">C2*D2</f>
-        <v>6.41</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="E8" s="6">
+        <v>3.89</v>
+      </c>
+      <c r="F8" s="6">
+        <f>D8*E8</f>
+        <v>3.89</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="2">
-        <v>1</v>
-      </c>
-      <c r="D3" s="6">
-        <v>14.46</v>
-      </c>
-      <c r="E3" s="6">
-        <f t="shared" si="0"/>
-        <v>14.46</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1</v>
-      </c>
-      <c r="D4" s="6">
-        <v>12.25</v>
-      </c>
-      <c r="E4" s="6">
-        <f t="shared" si="0"/>
-        <v>12.25</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-    </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-      <c r="D5" s="6">
-        <v>7.76</v>
-      </c>
-      <c r="E5" s="6">
-        <f>C5*D5</f>
-        <v>7.76</v>
-      </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="5"/>
-    </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1</v>
-      </c>
-      <c r="D6" s="6">
-        <v>4.4800000000000004</v>
-      </c>
-      <c r="E6" s="6">
-        <f>C6*D6</f>
-        <v>4.4800000000000004</v>
-      </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    </row>
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="2">
-        <v>1</v>
-      </c>
-      <c r="D7" s="6">
-        <v>4.99</v>
-      </c>
-      <c r="E7" s="6">
-        <f>C7*D7</f>
-        <v>4.99</v>
-      </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" s="5"/>
-    </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="2">
-        <v>1</v>
-      </c>
-      <c r="D8" s="6">
-        <v>3.89</v>
-      </c>
-      <c r="E8" s="6">
-        <f>C8*D8</f>
-        <v>3.89</v>
-      </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="D9" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="E9" s="6">
+        <v>9.98</v>
+      </c>
+      <c r="F9" s="6">
+        <f>D9*E9</f>
+        <v>9.98E-2</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="5"/>
+      <c r="K9" s="3"/>
       <c r="L9" s="5"/>
-    </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M9" s="5"/>
+    </row>
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="6"/>
+      <c r="D10" s="2"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G10" s="6"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="5"/>
+    </row>
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="6"/>
+      <c r="D11" s="2"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G11" s="6"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="6"/>
+      <c r="D12" s="2"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="5"/>
-    </row>
-    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G12" s="6"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="6"/>
+      <c r="D13" s="2"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
-      <c r="G13" s="3"/>
+      <c r="G13" s="6"/>
       <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
-      <c r="D14" s="6"/>
+      <c r="D14" s="2"/>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G14" s="6"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="6"/>
+      <c r="D15" s="2"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G15" s="6"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
-      <c r="D16" s="6"/>
+      <c r="D16" s="2"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="5"/>
-    </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G16" s="6"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
-      <c r="D17" s="6"/>
+      <c r="D17" s="2"/>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="5"/>
-    </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G17" s="6"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="6"/>
+      <c r="D18" s="2"/>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="5"/>
-    </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G18" s="6"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="5"/>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
-      <c r="D19" s="6"/>
+      <c r="D19" s="2"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="5"/>
-    </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G19" s="6"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="5"/>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
-      <c r="D20" s="6"/>
+      <c r="D20" s="2"/>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="5"/>
-    </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G20" s="6"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="5"/>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
-      <c r="D21" s="6"/>
+      <c r="D21" s="2"/>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="5"/>
-    </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G21" s="6"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="5"/>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="6"/>
+      <c r="D22" s="2"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="5"/>
-    </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G22" s="6"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="5"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
-      <c r="D23" s="6"/>
+      <c r="D23" s="2"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="5"/>
-    </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G23" s="6"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="5"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="6"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="7"/>
       <c r="F24" s="6"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="5"/>
-    </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G24" s="6"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="5"/>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2"/>
       <c r="B25" s="5"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="6"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="2"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="5"/>
-    </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G25" s="6"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="5"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
-      <c r="D26" s="6"/>
+      <c r="D26" s="2"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="5"/>
-    </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G26" s="6"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="5"/>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
-      <c r="D27" s="6"/>
+      <c r="D27" s="2"/>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
-      <c r="G27" s="3"/>
+      <c r="G27" s="6"/>
       <c r="H27" s="3"/>
-      <c r="I27" s="5"/>
-    </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I27" s="3"/>
+      <c r="J27" s="5"/>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
-      <c r="D28" s="6"/>
+      <c r="D28" s="2"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
-      <c r="G28" s="4"/>
-    </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G28" s="6"/>
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
-      <c r="D29" s="6"/>
+      <c r="D29" s="2"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="5"/>
-    </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G29" s="6"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="5"/>
+    </row>
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
-      <c r="D30" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="6">
-        <f>SUM(E2:E29)</f>
-        <v>54.24</v>
-      </c>
-      <c r="F30" s="6"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="5"/>
-    </row>
-    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D30" s="2"/>
+      <c r="E30" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="6">
+        <f>SUM(F2:F29)</f>
+        <v>25.131580000000003</v>
+      </c>
+      <c r="G30" s="6"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="5"/>
+    </row>
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
-      <c r="D31" s="6"/>
+      <c r="D31" s="2"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="5"/>
-    </row>
-    <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G31" s="6"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="5"/>
+    </row>
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
-      <c r="E32" s="6"/>
+      <c r="E32" s="2"/>
       <c r="F32" s="6"/>
-      <c r="G32" s="3"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G32" s="6"/>
+      <c r="H32" s="3"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
-      <c r="G33" s="3"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G33" s="2"/>
+      <c r="H33" s="3"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
-      <c r="G34" s="3"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G34" s="2"/>
+      <c r="H34" s="3"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="2"/>
-      <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
-      <c r="G35" s="1"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G4" r:id="rId1" xr:uid="{A2E1C8C8-6A04-46E2-AC51-28CA639AB5C3}"/>
-    <hyperlink ref="G3" r:id="rId2" xr:uid="{DF7A5359-89D1-4378-AEAB-FD422BE4C122}"/>
-    <hyperlink ref="G5" r:id="rId3" xr:uid="{3552A92A-EFA4-4FB0-92CC-E82180001E88}"/>
-    <hyperlink ref="H6" r:id="rId4" xr:uid="{FA8CF8E9-26AB-43B4-820A-5FF0ECE212F3}"/>
-    <hyperlink ref="G6" r:id="rId5" xr:uid="{B0CFF966-AF61-4A69-82E7-3D5DCE98FD10}"/>
-    <hyperlink ref="G2" r:id="rId6" xr:uid="{4C1B4732-A388-4A05-ACD7-7F60A4FA52BC}"/>
-    <hyperlink ref="G7" r:id="rId7" xr:uid="{A34649B7-C9A8-4DBC-80D3-EB9A1FEFCAB2}"/>
-    <hyperlink ref="G8" r:id="rId8" xr:uid="{7EEE3C29-E311-470E-A566-3FAB362B9E20}"/>
+    <hyperlink ref="H4" r:id="rId1" xr:uid="{A2E1C8C8-6A04-46E2-AC51-28CA639AB5C3}"/>
+    <hyperlink ref="H3" r:id="rId2" xr:uid="{DF7A5359-89D1-4378-AEAB-FD422BE4C122}"/>
+    <hyperlink ref="H5" r:id="rId3" xr:uid="{3552A92A-EFA4-4FB0-92CC-E82180001E88}"/>
+    <hyperlink ref="I6" r:id="rId4" xr:uid="{FA8CF8E9-26AB-43B4-820A-5FF0ECE212F3}"/>
+    <hyperlink ref="H6" r:id="rId5" xr:uid="{B0CFF966-AF61-4A69-82E7-3D5DCE98FD10}"/>
+    <hyperlink ref="H2" r:id="rId6" xr:uid="{4C1B4732-A388-4A05-ACD7-7F60A4FA52BC}"/>
+    <hyperlink ref="H7" r:id="rId7" xr:uid="{A34649B7-C9A8-4DBC-80D3-EB9A1FEFCAB2}"/>
+    <hyperlink ref="H8" r:id="rId8" xr:uid="{7EEE3C29-E311-470E-A566-3FAB362B9E20}"/>
+    <hyperlink ref="H9" r:id="rId9" display="https://www.homedepot.com/p/Gorilla-8-oz-Original-Glue-50008A/100204163" xr:uid="{3687080D-7764-4AE9-84DA-09203FC30570}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId9"/>
+  <pageSetup orientation="portrait" r:id="rId10"/>
 </worksheet>
 </file>
--- a/SYS_DEV/Columbia/V0/V0.7/v0.7.0/BOM-SPECIES-Columbia-v0.7.0.xlsx
+++ b/SYS_DEV/Columbia/V0/V0.7/v0.7.0/BOM-SPECIES-Columbia-v0.7.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slm30\Documents\GitHub\Smart-Penetrometer-with-Edge-Computing-and-Intelligent-Embedded-Systems\SYS_DEV\Columbia\V0\V0.7\v0.7.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Smart-Penetrometer-with-Edge-Computing-and-Intelligent-Embedded-Systems\SYS_DEV\Columbia\V0\V0.7\v0.7.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC6B2ED-1071-43B9-908B-581C1DE2BB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D57FC3C6-30BF-49BA-8AE3-593B8E8FC7E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="28680" yWindow="-150" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
   <si>
     <t>Total Cost</t>
   </si>
@@ -116,27 +116,9 @@
     <t xml:space="preserve">Slides onto the plastic tube easily. </t>
   </si>
   <si>
-    <t>https://www.harborfreight.com/high-strength-super-glue-10-pack-68345.html</t>
-  </si>
-  <si>
-    <t>HFT High-Strength Super Glue</t>
-  </si>
-  <si>
-    <t>https://www.grainger.com/product/SUPER-GLUE-Instant-Adhesive-Future-Glue-3EHP8</t>
-  </si>
-  <si>
-    <t>SUPER GLUE Instant Adhesive: Future Glue, Gen Purpose, 0.17 fl oz</t>
-  </si>
-  <si>
-    <t>Super Glue</t>
-  </si>
-  <si>
     <t>outer brass tube - spike probe</t>
   </si>
   <si>
-    <t>inner brass tube - spike probe</t>
-  </si>
-  <si>
     <t>abs tube - spike probe</t>
   </si>
   <si>
@@ -159,6 +141,12 @@
   </si>
   <si>
     <t>Amount in Inventory</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/GORILLA-Glue-Gen-Purpose-1TMA1</t>
+  </si>
+  <si>
+    <t>inner brass rod - spike probe</t>
   </si>
 </sst>
 </file>
@@ -585,25 +573,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:M35"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:M33"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="79.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="79.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.26953125" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
     <col min="7" max="7" width="41" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="99.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="99.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="76" customWidth="1"/>
-    <col min="10" max="10" width="83.54296875" customWidth="1"/>
-    <col min="11" max="11" width="62.54296875" customWidth="1"/>
-    <col min="12" max="12" width="55.81640625" customWidth="1"/>
+    <col min="10" max="10" width="83.5703125" customWidth="1"/>
+    <col min="11" max="11" width="62.5703125" customWidth="1"/>
+    <col min="12" max="12" width="55.85546875" customWidth="1"/>
     <col min="13" max="13" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
@@ -611,10 +599,10 @@
         <v>2</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>3</v>
@@ -644,9 +632,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>24</v>
@@ -671,9 +659,9 @@
       <c r="I2" s="5"/>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>16</v>
@@ -696,9 +684,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>13</v>
@@ -723,9 +711,9 @@
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
     </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>18</v>
@@ -748,7 +736,7 @@
       <c r="I5" s="3"/>
       <c r="J5" s="5"/>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
@@ -774,84 +762,61 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="5"/>
+      <c r="C7" s="2"/>
       <c r="D7" s="2">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="E7" s="6">
-        <v>4.99</v>
+        <v>9.98</v>
       </c>
       <c r="F7" s="6">
         <f>D7*E7</f>
-        <v>4.99</v>
-      </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="5"/>
-    </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>29</v>
-      </c>
+        <v>9.98E-2</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+    </row>
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="2">
-        <v>1</v>
-      </c>
-      <c r="E8" s="6">
-        <v>3.89</v>
-      </c>
-      <c r="F8" s="6">
-        <f>D8*E8</f>
-        <v>3.89</v>
-      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
       <c r="G8" s="6"/>
-      <c r="H8" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="E9" s="6">
-        <v>9.98</v>
-      </c>
-      <c r="F9" s="6">
-        <f>D9*E9</f>
-        <v>9.98E-2</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-    </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D9" s="2"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -862,7 +827,7 @@
       <c r="H10" s="3"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -871,9 +836,9 @@
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="5"/>
-    </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -884,7 +849,7 @@
       <c r="H12" s="3"/>
       <c r="I12" s="5"/>
     </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -893,9 +858,9 @@
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -906,7 +871,7 @@
       <c r="H14" s="3"/>
       <c r="I14" s="5"/>
     </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -917,7 +882,7 @@
       <c r="H15" s="3"/>
       <c r="I15" s="5"/>
     </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -928,7 +893,7 @@
       <c r="H16" s="3"/>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -939,7 +904,7 @@
       <c r="H17" s="3"/>
       <c r="I17" s="5"/>
     </row>
-    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -950,7 +915,7 @@
       <c r="H18" s="3"/>
       <c r="I18" s="5"/>
     </row>
-    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -961,7 +926,7 @@
       <c r="H19" s="3"/>
       <c r="I19" s="5"/>
     </row>
-    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -972,7 +937,7 @@
       <c r="H20" s="3"/>
       <c r="I20" s="5"/>
     </row>
-    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -983,21 +948,21 @@
       <c r="H21" s="3"/>
       <c r="I21" s="5"/>
     </row>
-    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="6"/>
+      <c r="E22" s="7"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="3"/>
       <c r="I22" s="5"/>
     </row>
-    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
       <c r="D23" s="2"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
@@ -1005,29 +970,30 @@
       <c r="H23" s="3"/>
       <c r="I23" s="5"/>
     </row>
-    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="7"/>
+      <c r="E24" s="6"/>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="3"/>
       <c r="I24" s="5"/>
     </row>
-    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="5"/>
-    </row>
-    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I25" s="3"/>
+      <c r="J25" s="5"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -1035,10 +1001,9 @@
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="5"/>
-    </row>
-    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1047,20 +1012,25 @@
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="5"/>
-    </row>
-    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I27" s="5"/>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
+      <c r="E28" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="6">
+        <f>SUM(F2:F27)</f>
+        <v>16.251580000000001</v>
+      </c>
       <c r="G28" s="6"/>
-      <c r="H28" s="4"/>
-    </row>
-    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H28" s="3"/>
+      <c r="I28" s="5"/>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -1071,70 +1041,43 @@
       <c r="H29" s="3"/>
       <c r="I29" s="5"/>
     </row>
-    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" s="6">
-        <f>SUM(F2:F29)</f>
-        <v>25.131580000000003</v>
-      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="3"/>
-      <c r="I30" s="5"/>
-    </row>
-    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
       <c r="H31" s="3"/>
-      <c r="I31" s="5"/>
-    </row>
-    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
       <c r="H32" s="3"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
-      <c r="H33" s="3"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="3"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="1"/>
+      <c r="H33" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1144,11 +1087,10 @@
     <hyperlink ref="I6" r:id="rId4" xr:uid="{FA8CF8E9-26AB-43B4-820A-5FF0ECE212F3}"/>
     <hyperlink ref="H6" r:id="rId5" xr:uid="{B0CFF966-AF61-4A69-82E7-3D5DCE98FD10}"/>
     <hyperlink ref="H2" r:id="rId6" xr:uid="{4C1B4732-A388-4A05-ACD7-7F60A4FA52BC}"/>
-    <hyperlink ref="H7" r:id="rId7" xr:uid="{A34649B7-C9A8-4DBC-80D3-EB9A1FEFCAB2}"/>
-    <hyperlink ref="H8" r:id="rId8" xr:uid="{7EEE3C29-E311-470E-A566-3FAB362B9E20}"/>
-    <hyperlink ref="H9" r:id="rId9" display="https://www.homedepot.com/p/Gorilla-8-oz-Original-Glue-50008A/100204163" xr:uid="{3687080D-7764-4AE9-84DA-09203FC30570}"/>
+    <hyperlink ref="I7" r:id="rId7" display="https://www.homedepot.com/p/Gorilla-8-oz-Original-Glue-50008A/100204163" xr:uid="{3687080D-7764-4AE9-84DA-09203FC30570}"/>
+    <hyperlink ref="H7" r:id="rId8" xr:uid="{2DA22F02-0B2C-466B-8EB5-68D61876C27A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId10"/>
+  <pageSetup orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>
--- a/SYS_DEV/Columbia/V0/V0.7/v0.7.0/BOM-SPECIES-Columbia-v0.7.0.xlsx
+++ b/SYS_DEV/Columbia/V0/V0.7/v0.7.0/BOM-SPECIES-Columbia-v0.7.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Smart-Penetrometer-with-Edge-Computing-and-Intelligent-Embedded-Systems\SYS_DEV\Columbia\V0\V0.7\v0.7.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D57FC3C6-30BF-49BA-8AE3-593B8E8FC7E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AD5620-D63B-4800-8CD2-2459157146DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-150" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -74,9 +74,6 @@
     <t>https://www.grainger.com/product/ABS-Tube-Stock-3-ft-Lg-60CY12?opr=ODOH&amp;analytics=FM:Order%20History</t>
   </si>
   <si>
-    <t>https://www.grainger.com/product/360-Brass-Rod-1-4-in-Outside-803H36?opr=ILOF</t>
-  </si>
-  <si>
     <t>ABS Tube Stock: 3 ft Lg, 1/4 in Inside Dia, 1/2 in Outside Dia, 0.13 in Wall Thick, Opaque, Black</t>
   </si>
   <si>
@@ -86,9 +83,6 @@
     <t>longest piece with free shipping on USC contract</t>
   </si>
   <si>
-    <t>360 Brass Rod: 1/4 in Outside Dia, 4 ft Overall Lg, H02, Mill, 45,000 psi Yield Strength</t>
-  </si>
-  <si>
     <t>https://www.grainger.com/product/SHRINK-KON-Heat-Shrink-Tubing-0-75-in-3KH60?opr=ILOF</t>
   </si>
   <si>
@@ -147,6 +141,12 @@
   </si>
   <si>
     <t>inner brass rod - spike probe</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/360-Brass-Rod-1-4-in-Outside-803H35?opr=ILOF</t>
+  </si>
+  <si>
+    <t>360 Brass Rod: 1/4 in Outside Dia, 36 in Overall Lg, H02, Mill, 45,000 psi Yield Strength, Inch</t>
   </si>
 </sst>
 </file>
@@ -599,10 +599,10 @@
         <v>2</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>3</v>
@@ -611,7 +611,7 @@
         <v>0</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>4</v>
@@ -634,10 +634,10 @@
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2">
@@ -651,20 +651,20 @@
         <v>6.57</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2">
@@ -678,18 +678,18 @@
         <v>2.0562499999999999</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2">
@@ -703,7 +703,7 @@
         <v>2.26953</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>11</v>
@@ -713,10 +713,10 @@
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2">
@@ -731,17 +731,17 @@
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="5"/>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2">
@@ -756,18 +756,18 @@
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2">
@@ -781,13 +781,13 @@
         <v>9.98E-2</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -1082,15 +1082,14 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H4" r:id="rId1" xr:uid="{A2E1C8C8-6A04-46E2-AC51-28CA639AB5C3}"/>
-    <hyperlink ref="H3" r:id="rId2" xr:uid="{DF7A5359-89D1-4378-AEAB-FD422BE4C122}"/>
-    <hyperlink ref="H5" r:id="rId3" xr:uid="{3552A92A-EFA4-4FB0-92CC-E82180001E88}"/>
-    <hyperlink ref="I6" r:id="rId4" xr:uid="{FA8CF8E9-26AB-43B4-820A-5FF0ECE212F3}"/>
-    <hyperlink ref="H6" r:id="rId5" xr:uid="{B0CFF966-AF61-4A69-82E7-3D5DCE98FD10}"/>
-    <hyperlink ref="H2" r:id="rId6" xr:uid="{4C1B4732-A388-4A05-ACD7-7F60A4FA52BC}"/>
-    <hyperlink ref="I7" r:id="rId7" display="https://www.homedepot.com/p/Gorilla-8-oz-Original-Glue-50008A/100204163" xr:uid="{3687080D-7764-4AE9-84DA-09203FC30570}"/>
-    <hyperlink ref="H7" r:id="rId8" xr:uid="{2DA22F02-0B2C-466B-8EB5-68D61876C27A}"/>
+    <hyperlink ref="H5" r:id="rId2" xr:uid="{3552A92A-EFA4-4FB0-92CC-E82180001E88}"/>
+    <hyperlink ref="I6" r:id="rId3" xr:uid="{FA8CF8E9-26AB-43B4-820A-5FF0ECE212F3}"/>
+    <hyperlink ref="H6" r:id="rId4" xr:uid="{B0CFF966-AF61-4A69-82E7-3D5DCE98FD10}"/>
+    <hyperlink ref="H2" r:id="rId5" xr:uid="{4C1B4732-A388-4A05-ACD7-7F60A4FA52BC}"/>
+    <hyperlink ref="I7" r:id="rId6" display="https://www.homedepot.com/p/Gorilla-8-oz-Original-Glue-50008A/100204163" xr:uid="{3687080D-7764-4AE9-84DA-09203FC30570}"/>
+    <hyperlink ref="H7" r:id="rId7" xr:uid="{2DA22F02-0B2C-466B-8EB5-68D61876C27A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId9"/>
+  <pageSetup orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>